--- a/Documents/HackerRankProblems.xlsx
+++ b/Documents/HackerRankProblems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\renuk\PythonLearnings\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9570788-B6B4-4F39-9287-A8417DFC4E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5F76AA-C829-4034-9DA5-B23EAA977EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>https://www.hackerrank.com/challenges/py-if-else/problem?isFullScreen=true</t>
   </si>
   <si>
-    <t>C:\Users\renuk\PythonLearnings\Week 4\ifelse.py</t>
-  </si>
-  <si>
     <t>link</t>
   </si>
   <si>
@@ -45,7 +42,34 @@
     <t>https://www.hackerrank.com/challenges/python-arithmetic-operators/problem?isFullScreen=true</t>
   </si>
   <si>
-    <t>C:\Users\renuk\PythonLearnings\Week 4\arithmetic-operators.py</t>
+    <t>https://www.hackerrank.com/challenges/python-division/problem?isFullScreen=true</t>
+  </si>
+  <si>
+    <t>C:\Users\renuk\PythonLearnings\Week 4\3. python-division.py</t>
+  </si>
+  <si>
+    <t>C:\Users\renuk\PythonLearnings\Week 4\1. ifelse.py</t>
+  </si>
+  <si>
+    <t>C:\Users\renuk\PythonLearnings\Week 4\2. arithmetic-operators.py</t>
+  </si>
+  <si>
+    <t>https://www.hackerrank.com/challenges/python-loops/problem?isFullScreen=true</t>
+  </si>
+  <si>
+    <t>C:\Users\renuk\PythonLearnings\Week 4\4. python-loops.py</t>
+  </si>
+  <si>
+    <t>https://www.hackerrank.com/challenges/write-a-function/problem?isFullScreen=true</t>
+  </si>
+  <si>
+    <t>C:\Users\renuk\PythonLearnings\Week 4\5. leap-year.py</t>
+  </si>
+  <si>
+    <t>https://www.hackerrank.com/challenges/python-print/problem?isFullScreen=true</t>
+  </si>
+  <si>
+    <t>C:\Users\renuk\PythonLearnings\Week 4\6. print-consecutive.py</t>
   </si>
 </sst>
 </file>
@@ -388,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -405,13 +429,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -422,7 +446,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -430,15 +454,67 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Documents/HackerRankProblems.xlsx
+++ b/Documents/HackerRankProblems.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\renuk\PythonLearnings\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5F76AA-C829-4034-9DA5-B23EAA977EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DE91B0-30AA-481F-AAD8-11CFDFDB6824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>https://www.hackerrank.com/challenges/py-if-else/problem?isFullScreen=true</t>
   </si>
@@ -70,6 +70,18 @@
   </si>
   <si>
     <t>C:\Users\renuk\PythonLearnings\Week 4\6. print-consecutive.py</t>
+  </si>
+  <si>
+    <t>https://www.hackerrank.com/challenges/list-comprehensions/problem?isFullScreen=true</t>
+  </si>
+  <si>
+    <t>C:\Users\renuk\PythonLearnings\Week 5\1. list-comprehensions.py</t>
+  </si>
+  <si>
+    <t>https://www.hackerrank.com/challenges/find-second-maximum-number-in-a-list/problem?isFullScreen=true</t>
+  </si>
+  <si>
+    <t>C:\Users\renuk\PythonLearnings\Week 5\2. find-second-maximum-number-in-a-list.py</t>
   </si>
 </sst>
 </file>
@@ -412,12 +424,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="91.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="101.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -511,10 +523,40 @@
         <v>14</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A10:C10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
